--- a/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/451185_2.xlsx
+++ b/tests/regression_artifacts/downloads/email_TSCW18489131_budget_marine_grenada/current/451185_2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Invoice Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="inlineStr"/>
@@ -757,7 +757,7 @@
         <v>28.82</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>28.82</v>
+        <v>778.14</v>
       </c>
       <c r="Q2" s="3">
         <f>O2*K2</f>
@@ -768,7 +768,7 @@
         <v/>
       </c>
       <c r="S2" s="3" t="n">
-        <v>30.84</v>
+        <v>832.61</v>
       </c>
       <c r="T2" s="3" t="n">
         <v>0</v>
@@ -777,7 +777,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>2.02</v>
+        <v>54.47</v>
       </c>
       <c r="W2" s="3" t="n">
         <v>0</v>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="AL2" t="n">
-        <v>1.45</v>
+        <v>39.24</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.54</v>
+        <v>14.6</v>
       </c>
     </row>
     <row r="3">
@@ -1073,7 +1073,7 @@
       <c r="N9" s="7" t="n"/>
       <c r="O9" s="7" t="n"/>
       <c r="P9" s="9" t="n">
-        <v>30.84</v>
+        <v>832.61</v>
       </c>
       <c r="Q9" s="7" t="n"/>
       <c r="R9" s="7" t="n"/>
@@ -1118,7 +1118,7 @@
       <c r="N10" s="7" t="n"/>
       <c r="O10" s="7" t="n"/>
       <c r="P10" s="9" t="n">
-        <v>83.79000000000001</v>
+        <v>2262.12</v>
       </c>
       <c r="Q10" s="7" t="n"/>
       <c r="R10" s="7" t="n"/>
@@ -1163,7 +1163,7 @@
       <c r="N11" s="7" t="n"/>
       <c r="O11" s="7" t="n"/>
       <c r="P11" s="9" t="n">
-        <v>4.19</v>
+        <v>113.11</v>
       </c>
       <c r="Q11" s="7" t="n"/>
       <c r="R11" s="7" t="n"/>
@@ -1208,7 +1208,7 @@
       <c r="N12" s="7" t="n"/>
       <c r="O12" s="7" t="n"/>
       <c r="P12" s="9" t="n">
-        <v>5.03</v>
+        <v>135.73</v>
       </c>
       <c r="Q12" s="7" t="n"/>
       <c r="R12" s="7" t="n"/>
@@ -1253,7 +1253,7 @@
       <c r="N13" s="7" t="n"/>
       <c r="O13" s="7" t="n"/>
       <c r="P13" s="9" t="n">
-        <v>13.95</v>
+        <v>376.64</v>
       </c>
       <c r="Q13" s="7" t="n"/>
       <c r="R13" s="7" t="n"/>
@@ -1298,7 +1298,7 @@
       <c r="N14" s="10" t="n"/>
       <c r="O14" s="10" t="n"/>
       <c r="P14" s="11" t="n">
-        <v>23.17</v>
+        <v>625.48</v>
       </c>
       <c r="Q14" s="10" t="n"/>
       <c r="R14" s="10" t="n"/>
@@ -1343,7 +1343,7 @@
       <c r="N15" s="7" t="n"/>
       <c r="O15" s="7" t="n"/>
       <c r="P15" s="12" t="n">
-        <v>0.2765246449456976</v>
+        <v>0.2765016886814139</v>
       </c>
       <c r="Q15" s="7" t="n"/>
       <c r="R15" s="7" t="n"/>
